--- a/Normalizacion_localidades.xlsx
+++ b/Normalizacion_localidades.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Antonio\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Antonio\Documents\MiProyectoGitHub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CE052F6-0709-467F-8552-AA204EE8B330}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{592AEB4F-8552-4566-BA89-F59FD2B82C85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="104">
   <si>
     <t>huercal</t>
   </si>
@@ -306,43 +306,37 @@
     <t>giralda</t>
   </si>
   <si>
-    <t>Adra</t>
-  </si>
-  <si>
-    <t>Berja</t>
-  </si>
-  <si>
-    <t>Velez</t>
-  </si>
-  <si>
-    <t>Cadiz</t>
-  </si>
-  <si>
     <t xml:space="preserve">st. mary's port; </t>
   </si>
   <si>
-    <t>Santa maria</t>
-  </si>
-  <si>
-    <t>Tarifa</t>
-  </si>
-  <si>
-    <t>Xerez</t>
-  </si>
-  <si>
-    <t>Xeres</t>
-  </si>
-  <si>
-    <t>Jerez</t>
-  </si>
-  <si>
     <t>sherry</t>
   </si>
   <si>
-    <t>Baena</t>
-  </si>
-  <si>
-    <t>Córdoba</t>
+    <t>xerez</t>
+  </si>
+  <si>
+    <t>xeres</t>
+  </si>
+  <si>
+    <t>jerez</t>
+  </si>
+  <si>
+    <t>santa maria</t>
+  </si>
+  <si>
+    <t>cadiz</t>
+  </si>
+  <si>
+    <t>tarifa</t>
+  </si>
+  <si>
+    <t>torre del oro</t>
+  </si>
+  <si>
+    <t>gold tower</t>
+  </si>
+  <si>
+    <t xml:space="preserve">torre del oro </t>
   </si>
 </sst>
 </file>
@@ -760,7 +754,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B72"/>
+  <dimension ref="A1:B74"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.88671875" customWidth="1"/>
@@ -780,7 +774,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>93</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -796,7 +790,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>94</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -820,7 +814,7 @@
         <v>10</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>95</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -844,7 +838,7 @@
         <v>14</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -860,7 +854,7 @@
         <v>17</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -881,10 +875,10 @@
     </row>
     <row r="15" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -892,7 +886,7 @@
         <v>19</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -900,7 +894,7 @@
         <v>19</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -908,7 +902,7 @@
         <v>19</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -916,7 +910,7 @@
         <v>19</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -929,7 +923,7 @@
     </row>
     <row r="21" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="7" t="s">
-        <v>104</v>
+        <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>20</v>
@@ -945,7 +939,7 @@
     </row>
     <row r="23" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
-        <v>105</v>
+        <v>21</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>22</v>
@@ -1337,9 +1331,25 @@
     </row>
     <row r="72" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A72" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A73" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A74" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="B72" s="1" t="s">
+      <c r="B74" s="1" t="s">
         <v>83</v>
       </c>
     </row>

--- a/Normalizacion_localidades.xlsx
+++ b/Normalizacion_localidades.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Antonio\Documents\MiProyectoGitHub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{592AEB4F-8552-4566-BA89-F59FD2B82C85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{793E3E74-15C7-4D43-AC0F-10EC36968B61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="96">
   <si>
     <t>huercal</t>
   </si>
@@ -222,21 +222,12 @@
     <t>villacarillo</t>
   </si>
   <si>
-    <t>vilacarillo</t>
-  </si>
-  <si>
     <t>antequera</t>
   </si>
   <si>
     <t>archidona</t>
   </si>
   <si>
-    <t>cártama</t>
-  </si>
-  <si>
-    <t>cartama</t>
-  </si>
-  <si>
     <t>málaga</t>
   </si>
   <si>
@@ -285,27 +276,9 @@
     <t>spanish</t>
   </si>
   <si>
-    <t>mosque</t>
-  </si>
-  <si>
-    <t>alhambra</t>
-  </si>
-  <si>
     <t>generalife</t>
   </si>
   <si>
-    <t xml:space="preserve">málaga </t>
-  </si>
-  <si>
-    <t>gibralfaro</t>
-  </si>
-  <si>
-    <t>tajo</t>
-  </si>
-  <si>
-    <t>giralda</t>
-  </si>
-  <si>
     <t xml:space="preserve">st. mary's port; </t>
   </si>
   <si>
@@ -330,13 +303,16 @@
     <t>tarifa</t>
   </si>
   <si>
-    <t>torre del oro</t>
-  </si>
-  <si>
-    <t>gold tower</t>
-  </si>
-  <si>
-    <t xml:space="preserve">torre del oro </t>
+    <t>cordoba</t>
+  </si>
+  <si>
+    <t>algarrobo</t>
+  </si>
+  <si>
+    <t>santiponce</t>
+  </si>
+  <si>
+    <t>italica</t>
   </si>
 </sst>
 </file>
@@ -754,7 +730,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B74"/>
+  <dimension ref="A1:B71"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.88671875" customWidth="1"/>
@@ -763,10 +739,10 @@
   <sheetData>
     <row r="1" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -838,7 +814,7 @@
         <v>14</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -854,7 +830,7 @@
         <v>17</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -862,7 +838,7 @@
         <v>17</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -875,10 +851,10 @@
     </row>
     <row r="15" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -886,7 +862,7 @@
         <v>19</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -894,7 +870,7 @@
         <v>19</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -902,7 +878,7 @@
         <v>19</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -910,7 +886,7 @@
         <v>19</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -950,71 +926,71 @@
         <v>21</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>86</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>23</v>
+        <v>92</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="B28" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="6" t="s">
+    <row r="29" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="B29" s="2" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="29" spans="1:2" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="1" t="s">
+    <row r="30" spans="1:2" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="B30" s="1" t="s">
         <v>30</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -1022,7 +998,7 @@
         <v>34</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>87</v>
+        <v>34</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -1030,7 +1006,7 @@
         <v>34</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -1206,82 +1182,82 @@
         <v>64</v>
       </c>
       <c r="B56" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A57" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A58" s="1" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="57" spans="1:2" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="1" t="s">
-        <v>67</v>
-      </c>
       <c r="B58" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="59" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A59" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="60" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A60" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="61" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A61" s="1" t="s">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
     </row>
     <row r="62" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A62" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A63" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A64" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="B62" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="1" t="s">
+      <c r="B64" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B63" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>91</v>
-      </c>
     </row>
     <row r="65" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="6" t="s">
+      <c r="A65" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="B65" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B65" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A66" s="1" t="s">
         <v>75</v>
       </c>
@@ -1299,58 +1275,34 @@
     </row>
     <row r="68" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A68" s="1" t="s">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
     </row>
     <row r="69" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A69" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="70" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A70" s="1" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="71" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A71" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A74" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
